--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:45</t>
+    <t xml:space="preserve">2026-09-10 00:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:53</t>
+    <t xml:space="preserve">2026-09-18 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:02</t>
+    <t xml:space="preserve">2026-09-23 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:23</t>
+    <t xml:space="preserve">2026-10-02 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:41</t>
+    <t xml:space="preserve">2026-10-05 14:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
